--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0015.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0015.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc Stage 2 Sát Thương</t>
+          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc Giai Đoạn 2 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc Stage 3 Sát Thương</t>
+          <t>Lời Kiếm Răn Dạy: Tranh Thuỷ Mặc Giai Đoạn 3 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Lên Tiếng: Stage 4 DMG Thuỷ Mặc</t>
+          <t>Lưỡi Kiếm Lên Tiếng: Sát Thương Giai Đoạn 4 Thuỷ Mặc</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Lên Tiếng: Sát Thương Dạy Dỗ</t>
+          <t>Lưỡi Kiếm Lên Tiếng: To Teach DMG</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Lên Tiếng: Sát Thương Cứu Rỗi</t>
+          <t>Lưỡi Kiếm Lên Tiếng: To Save DMG</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Lên Tiếng: Sát Thương Hy Sinh</t>
+          <t>Lưỡi Kiếm Lên Tiếng: To Sacrifice DMG</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>DMG Zephyr Song</t>
+          <t>Sát Thương Bản Giao Hưởng Zephyr</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>DMG Juggle</t>
+          <t>Sát Thương Tung Tăng</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>DMG Stormy Strike</t>
+          <t>Sát Thương Đòn Đánh Bão Tố</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Sát Thương Giải Phóng Feather</t>
+          <t>Sát Thương Giải Phóng Lông Vũ</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 5</t>
+          <t>Sát Thương Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>DMG Windborne Strike</t>
+          <t>Sát Thương Đòn Tấn Công Gió Bay</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sát Thương Chém Abyssal</t>
+          <t>Sát Thương Chém Vực Sâu</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Sát Thương Ngọn Cờ Triumph</t>
+          <t>Sát Thương Ngọn Cờ Chiến Thắng</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Emerald Storm: Sát Thương Kết Cục</t>
+          <t>Bão Ngọc Lục Bảo: Sát Thương Kết Cục</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 1 Thương Long.</t>
+          <t>DMG Giai đoạn 1 Thương Long.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 2 Thương Long.</t>
+          <t>DMG Giai đoạn 2 Thương Long.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 3 Thương Long.</t>
+          <t>DMG Giai đoạn 3 Thương Long.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thời Gian Qingloong Mode</t>
+          <t>Thời Gian Chế Độ Thanh Long</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Giai đoạn 3 Basic Attack: Resolve</t>
+          <t>Cú Đòn Cơ Bản Hạng 3: Quyết Tâm</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Giai đoạn 4 Basic Attack: Resolve</t>
+          <t>Cú Đòn Cơ Bản Hạng 4: Quyết Tâm</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Giai đoạn 5 Basic Attack: Resolve</t>
+          <t>Cú Đòn Cơ Bản Hạng 5: Quyết Tâm</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Heavy Attack: Quyết Tâm</t>
+          <t>Đòn Heavy Attack: Quyết Tâm</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Windborne Strike: Resolve</t>
+          <t>Đòn Tấn Công Gió Bay: Giải Quyết</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Chém Abyssal: Giải Quyết</t>
+          <t>Chém Vực Sâu: Giải Quyết</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Dodge Counter: Resolve</t>
+          <t>Dodge Counter: Quyết Tâm</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Ngọn Cờ Triumph: Quyết Tâm</t>
+          <t>Ngọn Cờ Chiến Thắng: Quyết Tâm</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>DMG Chi Counter</t>
+          <t>Sát thương Khí: Phản kích</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>DMG Chi Parry</t>
+          <t>Sát Thương Phản Kích Chi</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Skill Concerto Regen</t>
+          <t>Hồi phục Concerto Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Chi Counter Concerto Regen</t>
+          <t>Hồi phục Khí: Bản giao hưởng phản kích</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Chi Parry Concerto Regen</t>
+          <t>Hồi Phục Khí Nhạc Phản Kích Chi</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Thời gian Wind Field</t>
+          <t>Thời Gian Tác Dụng Trường Gió</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Sát Thương Punch Đẩy</t>
+          <t>Sát Thương Đấm Đẩy</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>DMG liên tục Zhoutian Progress</t>
+          <t>Tổn thương liên tục theo tiến trình Chu Thiên</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>DMG Minor Zhoutian Shock</t>
+          <t>Sát thương sốc Minor Zhoutian</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>DMG Major Zhoutian: Inner Shock</t>
+          <t>Thiếu Tá Zhoutian: Sát Thương Sốc Nội Tại</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>DMG Major Zhoutian: Outer Shock</t>
+          <t>Thiếu Tá Zhoutian: Sát Thương Sốc Ngoại Vi</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>DMG Yielding Pull</t>
+          <t>Sát Thương Kéo Dồn</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Shield Zhoutian Hạ cuối chưa hoàn thiện</t>
+          <t>Khiên Zhoutian Hạ cuối chưa hoàn thiện</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Shield cuối Minor Zhoutian</t>
+          <t>Khiên cuối Minor Zhoutian</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8617,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>DMG Blade Flurry</t>
+          <t>Sát Thương Kiếm Vũ</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>DMG Razor Wind</t>
+          <t>Sát Thương Razor Gió</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Tiêu hao STA của Razor Wind</t>
+          <t>Chi Phí STA Razor Gió</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>DMG Awakening Gale</t>
+          <t>Sát Thương Bản Giao Hưởng Gió Thức Tỉnh</t>
         </is>
       </c>
     </row>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>DMG Skyfall Severance</t>
+          <t>Sát Thương Đoạn Tuyệt Skyfall</t>
         </is>
       </c>
     </row>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Cooldown Bản Giao Hưởng Gió Thức Tỉnh</t>
+          <t>Hồi Chiêu Bản Giao Hưởng Gió Thức Tỉnh</t>
         </is>
       </c>
     </row>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Awakening Gale Concerto Regen</t>
+          <t>Hồi Phục Bản Giao Hưởng Gió Thức Tỉnh</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -9527,7 +9527,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Dance Mưa Mây</t>
+          <t>Sát Thương Giai Đoạn 1 Vũ Điệu Mưa Mây</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Stage 2 DMG Dance Mưa Mây</t>
+          <t>Sát Thương Giai Đoạn 2 Vũ Điệu Mưa Mây</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Healing Dance Mưa Mây</t>
+          <t>Hồi Phục Vũ Điệu Mưa Mây</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10307,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 1 Unbound Flow</t>
+          <t>Khúc Tự Do Trôi Dạt - Giai Đoạn 1 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10372,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 2 Unbound Flow</t>
+          <t>Khúc Tự Do Trôi Dạt - Giai Đoạn 2 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Đoạn Tuyệt Skyfall</t>
+          <t>Thời gian hồi Chiêu Đoạn Tuyệt Skyfall</t>
         </is>
       </c>
     </row>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Skyfall Severance Concerto Regen</t>
+          <t>Khúc Tái Sinh Đoạn Tuyệt Skyfall</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -10827,7 +10827,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -10892,7 +10892,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Stage 1 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -11217,7 +11217,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Stage 2 DMG Mid-air Attack</t>
+          <t>Sát Thương Giai Đoạn 2 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Chi Phí STA Stage 1 Mid-air Attack</t>
+          <t>Chi Phí STA Giai Đoạn 1 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -11477,7 +11477,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Chi Phí STA Stage 2 Mid-air Attack</t>
+          <t>Chi Phí STA Giai Đoạn 2 Mid-air Attack</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>DMG Kỹ Năng Bản Giao Hưởng Tùy Ứng</t>
+          <t>Sát Thương Kỹ Năng Thơ Giao Hưởng Ứng Biến</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Concerto Regen Tương Tác Thành Công</t>
+          <t>Hồi Phục Giao Hưởng thành công</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>DMG Nhịp Giáng Tứ Trùng</t>
+          <t>Sát Thương Nhịp Bốn Lần</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>DMG Giao Hưởng: Chủ Âm</t>
+          <t>Khúc Thơ Giao Hưởng: Tonic DMG</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -12517,7 +12517,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Thu hồi Bóng Kiếm Attack 1 Trên Không 1</t>
+          <t>Thu hồi Bóng Kiếm Mid-air Attack 1</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 1 Basic Attack</t>
+          <t>DMG Giai đoạn 1 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -13947,7 +13947,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 2 Basic Attack</t>
+          <t>DMG Giai đoạn 2 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -14077,7 +14077,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Sát thương Giai đoạn 3 Basic Attack</t>
+          <t>DMG Giai đoạn 3 Basic Attack</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>DMG Giai đoạn 4 của Basic Attack</t>
+          <t>Sát Thương Cú Đòn Cơ Bản Hạng 4</t>
         </is>
       </c>
     </row>
@@ -14337,7 +14337,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>DMG Giai Đoạn 5 Basic Attack</t>
+          <t>Sát Thương Cú Đòn Cơ Bản Hạng 5</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -14597,7 +14597,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>DMG Tấn Công Hướng Lên</t>
+          <t>Sát Thương Đòn Chém Lên</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14727,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack Nâng Cao</t>
+          <t>Sát Thương Đòn Heavy Attack Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -14987,7 +14987,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Kiếm Khúc Freedom – Sát Thương</t>
+          <t>Kiếm Khúc Tự Do – Sát Thương</t>
         </is>
       </c>
     </row>
@@ -15117,7 +15117,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Sát thương Attack 1 Trên Không 1</t>
+          <t>DMG Mid-air Attack 1</t>
         </is>
       </c>
     </row>
@@ -15247,7 +15247,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Sát thương Mid-air Attack 2</t>
+          <t>DMG Mid-air Attack 2</t>
         </is>
       </c>
     </row>
@@ -15377,7 +15377,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Sát thương Mid-air Attack 3</t>
+          <t>DMG Mid-air Attack 3</t>
         </is>
       </c>
     </row>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>DMG Phá Vỡ Bão Tố</t>
+          <t>May Tempest Break the Tides DMG</t>
         </is>
       </c>
     </row>
@@ -15767,7 +15767,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>DMG Lưỡi Kiếm Bão Gào</t>
+          <t>Sát Thương Kiếm Khúc Giao Hưởng Bão Gào</t>
         </is>
       </c>
     </row>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Cooldown Lưỡi Kiếm Bão Gào</t>
+          <t>Kiếm Khúc Giao Hưởng Bão Gào Hạ Nhiệt</t>
         </is>
       </c>
     </row>
@@ -16547,7 +16547,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Concerto Regen Resonance Skill</t>
+          <t>Hồi Phục Bản Giao Hưởng</t>
         </is>
       </c>
     </row>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Concerto Regen Phá Vỡ Bão Tố</t>
+          <t>May Tempest Break the Tides Concerto Regen</t>
         </is>
       </c>
     </row>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Resonance Cost: Lời Nguyện Cầu Chân Thành</t>
+          <t>Chi Phí Cộng Hưởng: Lời Nguyện Cầu Chân Thành</t>
         </is>
       </c>
     </row>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Kiếm Ghi Dấu Dòng Thủy Triều – Concerto Regen</t>
+          <t>Kiếm Ghi Dấu Dòng Thủy Triều – Hồi Phục Concerto</t>
         </is>
       </c>
     </row>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Kiếm Khúc Freedom – Concerto Regen</t>
+          <t>Kiếm Khúc Tự Do – Hồi Phục Concerto</t>
         </is>
       </c>
     </row>
@@ -17457,7 +17457,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown: Lời Nguyện Cầu Chân Thành</t>
+          <t>Thời gian hồi Chiêu: Lời Nguyện Cầu Chân Thành</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Avatar Đang Hồi</t>
+          <t>Hóa Thân Đang Hồi</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Avatar - Fleurdelys</t>
+          <t>Hóa Thân - Fleurdelys</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17912,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -17977,7 +17977,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Chi Phí Thể Lực Heavy Attack Nâng Cao</t>
+          <t>Chi Phí STA Đòn Heavy Attack Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực Attack 1 Trên Không 1</t>
+          <t>Chi phí STA Mid-air Attack 1</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực Mid-air Attack 2</t>
+          <t>Chi phí STA Mid-air Attack 2</t>
         </is>
       </c>
     </row>
@@ -18172,7 +18172,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Chi phí Thể Lực Mid-air Attack 3</t>
+          <t>Chi phí STA Mid-air Attack 3</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Vòng Trăng - Attack 1 Basic 1 Sát Thương</t>
+          <t>Vòng Trăng - Basic Attack 1 Sát Thương</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Moonring - Dodge Counter</t>
+          <t>Vòng Trăng - Dodge Counter Tránh</t>
         </is>
       </c>
     </row>
@@ -18562,7 +18562,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>DMG Nhịp Nguồn Cội</t>
+          <t>Sát Thương Nhịp Nguyên Sơ</t>
         </is>
       </c>
     </row>
@@ -18627,7 +18627,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Cooldown Bản Giao Hưởng Nguồn Cội</t>
+          <t>Hồi Chiêu Bản Giao Hưởng Nguồn Cội</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Concerto Regen Nhịp Nguồn Cội</t>
+          <t>Hồi Phục Bản Giao Hưởng Nguồn Cội</t>
         </is>
       </c>
     </row>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Sát Thương Closing Refrain</t>
+          <t>Sát Thương Điệp Khúc Kết</t>
         </is>
       </c>
     </row>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Cooldown Đoạn Kết/Khúc Hoàn Tất Chưa Trọn</t>
+          <t>Thời gian hồi Kết Đoạn/Điệp Khúc Dở Dang</t>
         </is>
       </c>
     </row>
@@ -18887,7 +18887,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Concerto Regen Khúc Hoàn Tất Chưa Trọn</t>
+          <t>Khúc dạo đầu chưa trọn - Concerto Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>DMG Cung Ngoài Rìa</t>
+          <t>Sát Thương Khúc Giao Hưởng Vượt Biên</t>
         </is>
       </c>
     </row>
@@ -19017,7 +19017,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Khúc Giao Hưởng Vượt Biên</t>
+          <t>Thời gian hồi Chiêu Khúc Giao Hưởng Vượt Biên</t>
         </is>
       </c>
     </row>
@@ -19147,7 +19147,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Thời gian Lunar Cycle</t>
+          <t>Thời gian Chu kỳ Mặt Trăng</t>
         </is>
       </c>
     </row>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>DMG Flux - Moonbow</t>
+          <t>Thương tổn - Nguyệt Cung</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>DMG Flux - Moonring</t>
+          <t>Thương tổn - Nguyệt Hoàn</t>
         </is>
       </c>
     </row>
@@ -19342,7 +19342,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Cung Trăng - Sát Thương Attack 1 Basic 1</t>
+          <t>Cung Trăng - Sát Thương Basic Attack 1</t>
         </is>
       </c>
     </row>
@@ -19537,7 +19537,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>DMG Moonbow - Dodge Counter</t>
+          <t>Nguyệt Cung - Dodge Counter Tránh Sát Thương</t>
         </is>
       </c>
     </row>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Sát Thương Đòn Attack 1 Basic 1 - Moonbow Nâng Cao</t>
+          <t>Sát Thương Đòn Basic Attack 1 - Moonbow Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Sát Thương Basic Attack 2 - Moonbow Nâng Cao</t>
+          <t>Sát Thương Đòn Basic Attack 2 - Moonbow Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -19732,7 +19732,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Sát Thương Basic Attack 3 - Moonbow Nâng Cao</t>
+          <t>Sát Thương Đòn Basic Attack 3 - Moonbow Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Sát Thương Dodge Counter - Moonbow Nâng Cao</t>
+          <t>Sát Thương Dodge Counter Tránh - Moonbow Nâng Cao</t>
         </is>
       </c>
     </row>
@@ -19927,7 +19927,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Nguyệt Cung - Attack 1 Basic 1 Healing</t>
+          <t>Nguyệt Cung - Basic Attack 1 Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Nguyệt Cung - Basic Attack 2 Healing</t>
+          <t>Nguyệt Cung - Basic Attack 2 Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -20057,7 +20057,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Nguyệt Cung - Basic Attack 3 Healing</t>
+          <t>Nguyệt Cung - Basic Attack 3 Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -20122,7 +20122,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Nguyệt Cung - Dodge Counter Healing</t>
+          <t>Nguyệt Cung - Dodge Counter Tránh Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -20187,7 +20187,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Healing Khúc Giao Hưởng Vượt Biên</t>
+          <t>Hồi Phục Khúc Giao Hưởng Vượt Biên</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20252,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>DMG Viên Mãn Tuyệt Đối</t>
+          <t>Sát Thương Bão Hòa Tuyệt Đối</t>
         </is>
       </c>
     </row>
@@ -20317,7 +20317,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Healing Bão Hòa Tuyệt Đối</t>
+          <t>Hồi Phục Bão Hòa Tuyệt Đối</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20382,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Thời Gian Tác Động Vùng Full Moon</t>
+          <t>Thời Gian Tác Động Vùng Trăng Tròn</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20447,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Healing Vùng Full Moon</t>
+          <t>Hồi Phục Vùng Trăng Tròn</t>
         </is>
       </c>
     </row>
@@ -20512,7 +20512,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -20772,7 +20772,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Concerto Regen Closing Refrain</t>
+          <t>Hồi Phục Concerto Điệp Khúc Kết</t>
         </is>
       </c>
     </row>
@@ -20967,7 +20967,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>DMG Khúc Hoàn Tất Chưa Trọn</t>
+          <t>Sát Thương Điệp Khúc Chưa Hoàn</t>
         </is>
       </c>
     </row>
@@ -21032,7 +21032,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hồi Phục Thể Lực Vùng Full Moon</t>
+          <t>Hồi Phục STA Vùng Trăng Tròn</t>
         </is>
       </c>
     </row>
@@ -21227,7 +21227,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Cung Trăng - Hồi Extrac Concerto Bổ Sung Attack 1 Basic 1</t>
+          <t>Cung Trăng - Hồi Phục Concerto Bổ Sung Basic Attack 1</t>
         </is>
       </c>
     </row>
@@ -21292,7 +21292,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Nguyệt Cung - Basic Attack 2 Hồi Extrac Concerto Bổ Sung</t>
+          <t>Nguyệt Cung - Basic Attack 2 Hồi Phục Concerto Bổ Sung</t>
         </is>
       </c>
     </row>
@@ -21357,7 +21357,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Nguyệt Cung - Basic Attack 3 Hồi Extrac Concerto Bổ Sung</t>
+          <t>Nguyệt Cung - Basic Attack 3 Hồi Phục Concerto Bổ Sung</t>
         </is>
       </c>
     </row>
@@ -21422,7 +21422,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Nguyệt Cung - Dodge Counter Hồi Extrac Concerto Bổ Sung</t>
+          <t>Nguyệt Cung - Dodge Counter Tránh Hồi Phục Concerto Bổ Sung</t>
         </is>
       </c>
     </row>
@@ -21487,7 +21487,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Hồi Extrac Khúc Giao Hưởng Bổ Sung Vượt Biên</t>
+          <t>Hồi Phục Khúc Giao Hưởng Bổ Sung Vượt Biên</t>
         </is>
       </c>
     </row>
@@ -21552,7 +21552,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>STA Tiêu Hao Mỗi Giây Khi Đi Lang Thang</t>
+          <t>Chi phí STA mỗi giây khi Đi Lang Thang</t>
         </is>
       </c>
     </row>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Khoảng Thời Gian Vùng Full Moon</t>
+          <t>Khoảng Thời Gian Vùng Trăng Tròn</t>
         </is>
       </c>
     </row>
@@ -21682,7 +21682,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Heavy Attack - Tiêu hao Thể Lực dạng Dòng Chảy</t>
+          <t>Tấn Công Mạnh - Tiêu hao STA dạng Dòng Chảy</t>
         </is>
       </c>
     </row>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Light Vàng: Basic Attack</t>
+          <t>Ánh Sáng Vàng: Basic Attack</t>
         </is>
       </c>
     </row>
@@ -21812,7 +21812,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Glitter</t>
+          <t>Lấp Lánh</t>
         </is>
       </c>
     </row>
@@ -21877,7 +21877,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Light Vàng: Đòn Lao Xuống</t>
+          <t>Ánh Sáng Vàng: Tấn Công Lao Xuống</t>
         </is>
       </c>
     </row>
@@ -21942,7 +21942,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Light Đỏ: Sát Thương Attack 1 Basic 1</t>
+          <t>Ánh Sáng Đỏ: Sát Thương Basic Attack 1</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Light Đỏ: Sát Thương Basic Attack 2</t>
+          <t>Ánh Sáng Đỏ: Sát Thương Basic Attack 2</t>
         </is>
       </c>
     </row>
@@ -22072,7 +22072,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Light Đỏ: Sát Thương Basic Attack 3</t>
+          <t>Ánh Sáng Đỏ: Sát Thương Basic Attack 3</t>
         </is>
       </c>
     </row>
@@ -22137,7 +22137,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Light Đỏ: Sát Thương Heavy Attack</t>
+          <t>Ánh Sáng Đỏ: Heavy Attack DMG</t>
         </is>
       </c>
     </row>
@@ -22202,7 +22202,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Đèn Đỏ: Sát Thương Đòn Lao Xuống</t>
+          <t>Đèn Đỏ: Plunging Attack DMG</t>
         </is>
       </c>
     </row>
@@ -22267,7 +22267,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Light Vàng: Tốn STA Khi Lao Xuống</t>
+          <t>Ánh Sáng Vàng: Plunging Attack STA Cost</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Đèn Đỏ: Chi Phí Thể Lực Heavy Attack</t>
+          <t>Đèn Đỏ: Heavy Attack STA Cost</t>
         </is>
       </c>
     </row>
@@ -22397,7 +22397,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Đèn Đỏ: Chi Phí Thể Lực Đòn Lao Xuống</t>
+          <t>Đèn Đỏ: Plunging Attack STA Cost</t>
         </is>
       </c>
     </row>
@@ -22462,7 +22462,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>DMG Vồ Lấy</t>
+          <t>Sát Thương Vồ</t>
         </is>
       </c>
     </row>
@@ -22527,7 +22527,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>DMG Nảy Lên</t>
+          <t>Sát Thương Phản Đòn</t>
         </is>
       </c>
     </row>
@@ -22592,7 +22592,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>STA Tiêu Hao Vồ Lấy</t>
+          <t>Chi Phí STA Vồ</t>
         </is>
       </c>
     </row>
@@ -22657,7 +22657,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>STA Tiêu Hao Nảy Lên</t>
+          <t>Chi Phí STA Phản Đòn</t>
         </is>
       </c>
     </row>
@@ -22722,7 +22722,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -22787,7 +22787,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -23112,7 +23112,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>DMG Ánh Nhìn Chói Lóa</t>
+          <t>Sát Thương Chói Lóa</t>
         </is>
       </c>
     </row>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Đèn Sân Khấu Đỏ: Sát Thương Attack 1 Basic 1</t>
+          <t>Đèn Sân Khấu Đỏ: Sát Thương Basic Attack 1</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23372,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Đèn Sân Khấu Đỏ: Sát Thương Heavy Attack</t>
+          <t>Đèn Sân Khấu Đỏ: Heavy Attack DMG</t>
         </is>
       </c>
     </row>
@@ -23437,7 +23437,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>DMG Vồ Lấy Tăng Cường</t>
+          <t>Sát Thương Nhảy Tấn Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -23502,7 +23502,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>DMG Nảy Lên Tăng Cường</t>
+          <t>Sát Thương Khúc Nhạc Dội Lại Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -23567,7 +23567,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>DMG Tia Laser Đơn</t>
+          <t>Sát Thương Tia Laser Đơn</t>
         </is>
       </c>
     </row>
@@ -23632,7 +23632,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Light Đỏ: Sát Thương Dodge Counter</t>
+          <t>Ánh Sáng Đỏ: Dodge Counter DMG</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23697,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Concerto Regen Vồ Lấy Tăng Cường</t>
+          <t>Hồi Phục Nhạc Đoạn Vồ Lấy Đầy Hứng Khởi</t>
         </is>
       </c>
     </row>
@@ -23762,7 +23762,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Concerto Regen Nảy Lên Tăng Cường</t>
+          <t>Hồi Phục Khúc Nhạc Dội Lại Năng Lượng</t>
         </is>
       </c>
     </row>
@@ -23827,7 +23827,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -23892,7 +23892,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -23957,7 +23957,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -24022,7 +24022,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -24087,7 +24087,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -24152,7 +24152,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Sát Thương Plunging Attack</t>
+          <t>Sát Thương Tấn Công Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -24282,7 +24282,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -24347,7 +24347,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Tiêu Hao Thể Lực Plunging Attack</t>
+          <t>Tiêu Hao STA Tấn Công Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -24412,7 +24412,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Sát Thương Butterfly Sao Mờ</t>
+          <t>Sát Thương Bướm Sao Mờ</t>
         </is>
       </c>
     </row>
@@ -24477,7 +24477,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -24607,7 +24607,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -24802,7 +24802,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -24932,7 +24932,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Thời Gian Tồn Tại Stellarealm</t>
+          <t>Thời Gian Cõi Tinh Tú</t>
         </is>
       </c>
     </row>
@@ -25062,7 +25062,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -25192,7 +25192,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>DMG Giác Ngộ</t>
+          <t>Sát Thương Khai Sáng</t>
         </is>
       </c>
     </row>
@@ -25387,7 +25387,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>DMG Phân Biệt</t>
+          <t>Sát Thương Phán Đoán</t>
         </is>
       </c>
     </row>
@@ -25517,7 +25517,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Healing Khai Sáng</t>
+          <t>Hồi Phục Khai Sáng</t>
         </is>
       </c>
     </row>
@@ -25647,7 +25647,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Healing Phán Đoán</t>
+          <t>Hồi Phục Phán Đoán</t>
         </is>
       </c>
     </row>
@@ -25777,7 +25777,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Concerto Regen Giác Ngộ</t>
+          <t>Hồi Phục Bản Giao Hưởng Khai Sáng</t>
         </is>
       </c>
     </row>
@@ -25842,7 +25842,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Concerto Regen Phân Biệt</t>
+          <t>Hồi Phục Bản Giao Hưởng Phán Đoán</t>
         </is>
       </c>
     </row>
@@ -25907,7 +25907,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Sát Thương Butterfly Sao Lửa</t>
+          <t>Sát Thương Bướm Sao Lửa</t>
         </is>
       </c>
     </row>
@@ -25972,7 +25972,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>DMG Suy Luận</t>
+          <t>Sát Thương Giao Hưởng Illation</t>
         </is>
       </c>
     </row>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>DMG Biến Hóa</t>
+          <t>Sát Thương Biến Đổi</t>
         </is>
       </c>
     </row>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>STA Tiêu Hao Suy Luận</t>
+          <t>Chi Phí STA Giao Hưởng Illation</t>
         </is>
       </c>
     </row>
@@ -26167,7 +26167,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>STA Tiêu Hao Biến Hóa</t>
+          <t>Chi Phí STA Biến Đổi</t>
         </is>
       </c>
     </row>
@@ -26232,7 +26232,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Concerto Regen Suy Luận</t>
+          <t>Hồi Phục Giao Hưởng Illation</t>
         </is>
       </c>
     </row>
@@ -26297,7 +26297,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Concerto Regen Biến Hóa</t>
+          <t>Khúc Giao Hưởng Biến Đổi Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -26362,7 +26362,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -26492,7 +26492,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -26557,7 +26557,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -26622,7 +26622,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Heavy Attack: Sát Thương Sao Lóe</t>
+          <t>Đòn Heavy Attack: Starflash DMG</t>
         </is>
       </c>
     </row>
@@ -26752,7 +26752,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -26817,7 +26817,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>DMG Chamuel's Star: Dodge Counter</t>
+          <t>Sao Chamuel: Dodge Counter DMG</t>
         </is>
       </c>
     </row>
@@ -26882,7 +26882,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -26947,7 +26947,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Heavy Attack: Sao Lóe Tiêu Hao STA</t>
+          <t>Đòn Heavy Attack: Starflash STA Cost</t>
         </is>
       </c>
     </row>
@@ -27077,7 +27077,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -27142,7 +27142,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Ring of Mirrors: Sát Thương Light Thánh Khúc Xạ</t>
+          <t>Nhẫn Gương Phản Chiếu: Refracted Holy Light DMG</t>
         </is>
       </c>
     </row>
@@ -27272,7 +27272,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>DMG Chamuel's Star: Giai Đoạn 1</t>
+          <t>Sao Chamuel: DMG Giai đoạn 1</t>
         </is>
       </c>
     </row>
@@ -27337,7 +27337,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>DMG Chamuel's Star: Giai Đoạn 2</t>
+          <t>Sao Chamuel: Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -27402,7 +27402,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>DMG Chamuel's Star: Giai Đoạn 3</t>
+          <t>Sao Chamuel: Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -27467,7 +27467,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -27532,7 +27532,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -27597,7 +27597,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -27857,7 +27857,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -27987,7 +27987,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Heavy Attack: Sát Thương Sao Lóe</t>
+          <t>Đòn Heavy Attack: Starflash DMG</t>
         </is>
       </c>
     </row>
@@ -28052,7 +28052,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Heavy Attack: Sao Lóe Tiêu Hao STA</t>
+          <t>Đòn Heavy Attack: Starflash STA Cost</t>
         </is>
       </c>
     </row>
@@ -28117,7 +28117,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>DMG Kinh Cầu Xá Tội</t>
+          <t>Sát Thương Kinh Cầu Giải Tội</t>
         </is>
       </c>
     </row>
@@ -28182,7 +28182,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>DMG Lời Thú Tội Hoàn Toàn</t>
+          <t>Sát Thương Xưng Tội Hoàn Mỹ</t>
         </is>
       </c>
     </row>
@@ -28247,7 +28247,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Concerto Regen Kinh Cầu Xá Tội</t>
+          <t>Khúc Tụng Cầu Tha Thứ - Concerto Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -28312,7 +28312,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Concerto Regen Lời Thú Tội Hoàn Toàn</t>
+          <t>Khúc Tái Sinh Xưng Tội Hoàn Mỹ</t>
         </is>
       </c>
     </row>
@@ -28442,7 +28442,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -28507,7 +28507,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -28572,7 +28572,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Stage 3 DMG</t>
+          <t>Sát Thương Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -28637,7 +28637,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Stage 4 DMG</t>
+          <t>Sát Thương Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -28702,7 +28702,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>DMG Đột Phá</t>
+          <t>Sát Thương Đột Phá</t>
         </is>
       </c>
     </row>
@@ -28767,7 +28767,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -28832,7 +28832,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Sát Thương Plunging Attack</t>
+          <t>Sát Thương Tấn Công Đâm Xuống</t>
         </is>
       </c>
     </row>
@@ -28897,7 +28897,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -28962,7 +28962,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -29092,7 +29092,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>DMG Giao Thức Phòng Thủ Chuẩn</t>
+          <t>DMG Giao Thức Phòng Ngự Chuẩn</t>
         </is>
       </c>
     </row>
@@ -29157,7 +29157,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>DMG Đòn Đánh Chính Xác</t>
+          <t>Sát Thương Đòn Điểm Chính Xác</t>
         </is>
       </c>
     </row>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>DMG Hành Động Có Mục Tiêu</t>
+          <t>Sát Thương Bản Giao Hưởng Hành Động Có Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -29287,7 +29287,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>DMG Phản Đòn Cưỡng Chế</t>
+          <t>Sát Thương Phản Công Cưỡng Bách</t>
         </is>
       </c>
     </row>
@@ -29352,7 +29352,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Cooldown chiêu Giao Thức Defense Chuẩn</t>
+          <t>Thời gian hồi chiêu Giao Thức Phòng Ngự Chuẩn</t>
         </is>
       </c>
     </row>
@@ -29482,7 +29482,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Giao Hưởng Defense Tiêu Chuẩn - Concerto Regen</t>
+          <t>Giao Hưởng Phòng Ngự Tiêu Chuẩn - Hồi Phục Concerto</t>
         </is>
       </c>
     </row>
@@ -29547,7 +29547,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Concerto Regen Đòn Đánh Chính Xác</t>
+          <t>Khúc Giao Hưởng Tái Tạo Đòn Điểm Chính Xác</t>
         </is>
       </c>
     </row>
@@ -29612,7 +29612,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Concerto Regen Hành Động Có Mục Tiêu</t>
+          <t>Hồi Phục Bản Giao Hưởng Hành Động Có Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Concerto Regen của Forcible Riposte</t>
+          <t>Hồi Phục Khúc Phản Công Cưỡng Bách</t>
         </is>
       </c>
     </row>
@@ -29742,7 +29742,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Thời gian Sunburst</t>
+          <t>Thời Gian Ánh Dương Bùng Sáng</t>
         </is>
       </c>
     </row>
@@ -29872,7 +29872,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>DMG của Heavy Slash - Daybreak</t>
+          <t>Tấn Công Mạnh - Sát Thương Rạng Đông</t>
         </is>
       </c>
     </row>
@@ -29937,7 +29937,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>DMG của Heavy Slash - Dawning</t>
+          <t>Tấn Công Mạnh - Sát Thương Bình Minh</t>
         </is>
       </c>
     </row>
@@ -30002,7 +30002,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>DMG của Heavy Slash - Nightfall</t>
+          <t>Tấn Công Mạnh - Sát Thương Hoàng Hôn</t>
         </is>
       </c>
     </row>
@@ -30067,7 +30067,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Hệ số nhân bổ sung mỗi Blaze</t>
+          <t>Hệ số nhân bổ sung cho mỗi lần Blaze</t>
         </is>
       </c>
     </row>
@@ -30132,7 +30132,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>DMG của Heavy Slash - Lightsmash</t>
+          <t>Tấn Công Mạnh - Sát Thương Phá Tan Ánh Sáng</t>
         </is>
       </c>
     </row>
@@ -30197,7 +30197,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Tầng Heliacal Ember tối đa</t>
+          <t>Số Ngọn Lửa Heliacal tối đa</t>
         </is>
       </c>
     </row>
@@ -30262,7 +30262,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Thời gian Heliacal Ember mỗi tầng</t>
+          <t>Thời Gian Tồn Tại Của Heliacal Ember Mỗi Lớp</t>
         </is>
       </c>
     </row>
@@ -30392,7 +30392,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>DMG của Rekindle</t>
+          <t>Sát Thương Tái Sinh</t>
         </is>
       </c>
     </row>
@@ -30457,7 +30457,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>DMG của The Last Stand</t>
+          <t>Sát Thương Phòng Thủ Cuối Cùng</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30522,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Increase Hệ Số Basic Attack</t>
+          <t>Tăng Hệ Số Basic Attack</t>
         </is>
       </c>
     </row>
@@ -30587,7 +30587,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -30717,7 +30717,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -30782,7 +30782,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Concerto Regen của Rekindle</t>
+          <t>Khúc Giao Hưởng Tái Sinh</t>
         </is>
       </c>
     </row>
@@ -30847,7 +30847,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Concerto Regen của The Last Stand</t>
+          <t>Khúc Concerto Phòng Thủ Cuối Cùng - Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -30912,7 +30912,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Thời Gian Inferno Mode</t>
+          <t>Thời Gian Chế Độ Hỏa Ngục</t>
         </is>
       </c>
     </row>
@@ -31042,7 +31042,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -31172,7 +31172,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Stage 1 DMG</t>
+          <t>Sát Thương Giai Đoạn 1</t>
         </is>
       </c>
     </row>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Stage 2 DMG</t>
+          <t>Sát Thương Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -31302,7 +31302,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Sát Thương Của Death Snip</t>
+          <t>Sát Thương Của Cú Chém Tử Thần</t>
         </is>
       </c>
     </row>
@@ -31367,7 +31367,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Sát Thương Bổ Sung Của Death Snip</t>
+          <t>Sát Thương Bổ Sung Của Cú Chém Tử Thần</t>
         </is>
       </c>
     </row>
@@ -31432,7 +31432,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Healing Bằng Death Snip</t>
+          <t>Hồi Phục Bằng Cú Chém Tử Thần</t>
         </is>
       </c>
     </row>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -31562,7 +31562,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>DMG của Thread Withdrawn</t>
+          <t>Sát Thương Rút Lui</t>
         </is>
       </c>
     </row>
@@ -31627,7 +31627,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Sát Thương Rending Lunge</t>
+          <t>Sát Thương Đòn Lao Xé</t>
         </is>
       </c>
     </row>
@@ -31692,7 +31692,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Sát Thương Heavy Attack</t>
+          <t>Sát Thương Đòn Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -31822,7 +31822,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>DMG của Severed Facet</t>
+          <t>Sát Thương Mảnh Đoạn Tuyệt</t>
         </is>
       </c>
     </row>
@@ -31887,7 +31887,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>DMG của Hanging Finality</t>
+          <t>Sát Thương Định Mệnh Treo Lơ Lửng</t>
         </is>
       </c>
     </row>
@@ -31952,7 +31952,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Dodge Counter DMG</t>
+          <t>Sát Thương Né Tránh Phản Công</t>
         </is>
       </c>
     </row>
@@ -32017,7 +32017,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Eye of Unraveling - Sát Thương Thu Hồi</t>
+          <t>Con Mắt Giải Khai - Sát Thương Thu Hồi</t>
         </is>
       </c>
     </row>
@@ -32082,7 +32082,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Chi phí Thể lực cho Heavy Attack</t>
+          <t>Chi phí STA cho Heavy Attack</t>
         </is>
       </c>
     </row>
@@ -32212,7 +32212,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>STA Cost của Hanging Finality</t>
+          <t>Chi Phí STA Định Mệnh Treo Lơ Lửng</t>
         </is>
       </c>
     </row>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>STA Cost của Severed Facet</t>
+          <t>Chi Phí STA Mảnh Đoạn Tuyệt</t>
         </is>
       </c>
     </row>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>DMG của Eye of Unraveling</t>
+          <t>Sát Thương Con Mắt Giải Khai</t>
         </is>
       </c>
     </row>
@@ -32407,7 +32407,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>DMG của Serrated Loop</t>
+          <t>DMG Vòng Xẻ Rãnh</t>
         </is>
       </c>
     </row>
@@ -32472,7 +32472,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown Eye of Unraveling</t>
+          <t>Thời gian hồi Chiêu Con Mắt Giải Khai</t>
         </is>
       </c>
     </row>
@@ -32602,7 +32602,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Sát thương Giữ Vòng Xẻ Rãnh</t>
+          <t>DMG Giữ Vòng Xẻ Rãnh</t>
         </is>
       </c>
     </row>
@@ -32667,7 +32667,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Skill DMG</t>
+          <t>DMG Kỹ năng</t>
         </is>
       </c>
     </row>
@@ -32732,7 +32732,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
     </row>
@@ -32797,7 +32797,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>{0} Tấn Công</t>
+          <t>{0} ATK</t>
         </is>
       </c>
     </row>
@@ -32862,7 +32862,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -32992,7 +32992,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Resonance Cost</t>
+          <t>Chi Phí Cộng Hưởng</t>
         </is>
       </c>
     </row>
